--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_403_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_403_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>8</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>11</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1338,13 +1338,13 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>10</v>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>47:30</t>
+          <t>27:31</t>
         </is>
       </c>
       <c r="AN17" t="n">
@@ -1451,22 +1451,22 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>16.4%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
         <v>16</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>66:31</t>
+          <t>26:32</t>
         </is>
       </c>
       <c r="AN18" t="n">
@@ -1647,22 +1647,22 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>39.7%</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>28:18</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AN19" t="n">
@@ -1843,17 +1843,17 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
@@ -1923,7 +1923,7 @@
         <v>2</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>42:27</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AN20" t="n">
@@ -2039,17 +2039,17 @@
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
@@ -2119,16 +2119,16 @@
         <v>10</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>2</v>
@@ -2315,16 +2315,16 @@
         <v>16</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>8</v>
@@ -2511,16 +2511,16 @@
         <v>25</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>7</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>65:42</t>
+          <t>25:43</t>
         </is>
       </c>
       <c r="AN23" t="n">
@@ -2627,22 +2627,22 @@
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>21.3%</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>02:03</t>
         </is>
       </c>
       <c r="AN24" t="n">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>25:03</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AN25" t="n">
@@ -3019,22 +3019,22 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>23.8%</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -3167,7 +3167,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>32:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="AN26" t="n">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>15.3%</t>
         </is>
       </c>
     </row>
@@ -3301,10 +3301,10 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>45:13</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AN27" t="n">
@@ -3411,17 +3411,17 @@
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
@@ -3827,16 +3827,16 @@
         <v>110</v>
       </c>
       <c r="T30" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>36</v>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>05:46</t>
         </is>
       </c>
       <c r="AN35" t="n">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
@@ -4491,7 +4491,7 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>40:44</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AN36" t="n">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
@@ -4687,7 +4687,7 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>63:40</t>
+          <t>33:41</t>
         </is>
       </c>
       <c r="AN37" t="n">
@@ -4800,12 +4800,12 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4883,7 +4883,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>32:59</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AN38" t="n">
@@ -4996,17 +4996,17 @@
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
@@ -5076,16 +5076,16 @@
         <v>20</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
         <v>1</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>60:56</t>
+          <t>30:56</t>
         </is>
       </c>
       <c r="AN39" t="n">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>64.3%</t>
         </is>
       </c>
     </row>
@@ -5272,16 +5272,16 @@
         <v>-1</v>
       </c>
       <c r="T40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
         <v>3</v>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>48:46</t>
+          <t>28:47</t>
         </is>
       </c>
       <c r="AN40" t="n">
@@ -5388,22 +5388,22 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>7.5%</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>24:27</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AN42" t="n">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>27:33</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="AN43" t="n">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AN44" t="n">
@@ -6172,7 +6172,7 @@
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>32:34</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AN45" t="n">
@@ -6368,22 +6368,22 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>18.1%</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>00:24</t>
         </is>
       </c>
       <c r="AN46" t="n">
@@ -6784,16 +6784,16 @@
         <v>70</v>
       </c>
       <c r="T48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U48" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
         <v>17</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_403_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_403_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M2" t="n">
         <v>8</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
         <v>11</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1338,13 +1338,13 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X17" t="n">
         <v>10</v>
@@ -1531,7 +1531,7 @@
         <v>16</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
         <v>2</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2119,16 +2119,16 @@
         <v>10</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X21" t="n">
         <v>2</v>
@@ -2315,16 +2315,16 @@
         <v>16</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X22" t="n">
         <v>8</v>
@@ -2511,16 +2511,16 @@
         <v>25</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X23" t="n">
         <v>7</v>
@@ -3102,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -3301,10 +3301,10 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>110</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="X30" t="n">
         <v>36</v>
@@ -4488,10 +4488,10 @@
         <v>7</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -4687,7 +4687,7 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -4883,7 +4883,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -5076,16 +5076,16 @@
         <v>20</v>
       </c>
       <c r="T39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X39" t="n">
         <v>1</v>
@@ -5272,16 +5272,16 @@
         <v>-1</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X40" t="n">
         <v>3</v>
@@ -5471,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -6784,16 +6784,16 @@
         <v>70</v>
       </c>
       <c r="T48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X48" t="n">
         <v>17</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_403_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_403_EL.xlsx
@@ -674,10 +674,10 @@
         <v>8</v>
       </c>
       <c r="N2" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="O2" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>78.26</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>11</v>
       </c>
       <c r="N3" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="O3" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>56.67</t>
+          <t>45.83</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,14 +1347,14 @@
         <v>4</v>
       </c>
       <c r="X17" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA17" t="n">
@@ -1739,14 +1739,14 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA19" t="n">
@@ -2131,10 +2131,10 @@
         <v>2</v>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
@@ -2327,14 +2327,14 @@
         <v>3</v>
       </c>
       <c r="X22" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Y22" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="AA22" t="n">
@@ -2523,14 +2523,14 @@
         <v>3</v>
       </c>
       <c r="X23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA23" t="n">
@@ -3839,14 +3839,14 @@
         <v>13</v>
       </c>
       <c r="X30" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="Y30" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4500,14 +4500,14 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y36" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AA36" t="n">
@@ -4892,14 +4892,14 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA38" t="n">
@@ -5676,14 +5676,14 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA42" t="n">
@@ -6796,14 +6796,14 @@
         <v>2</v>
       </c>
       <c r="X48" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="Y48" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="AA48" t="n">
